--- a/config_Psychologie_2026_2027.xlsx
+++ b/config_Psychologie_2026_2027.xlsx
@@ -557,14 +557,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,11 +587,6 @@
           <t>criterium (optioneel)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>score_type</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -615,11 +609,6 @@
           <t>Vakkennis wiskunde</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -642,11 +631,6 @@
           <t>Vakkennis Engels</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -669,11 +653,6 @@
           <t>Vakkennis biologie</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -696,11 +675,6 @@
           <t>Profielsterkheid</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -723,11 +697,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -750,11 +719,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -777,11 +741,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -804,11 +763,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -831,11 +785,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -858,11 +807,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -885,11 +829,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -912,11 +851,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -939,11 +873,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -966,11 +895,6 @@
           <t>Vakkennis keuzevak</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -994,11 +918,6 @@
           <t>Algemeen studieniveau</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1017,11 +936,6 @@
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>punten (0-5)</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1044,11 +958,6 @@
           <t>Studiemotivatie</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>schaal 1-3</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1067,11 +976,6 @@
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1090,11 +994,6 @@
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
